--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Impediment-Log-S2.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Sprint 2/Impediment-Log-S2.xlsx
@@ -39,7 +39,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +64,11 @@
         <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -88,6 +93,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -560,8 +569,37 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="D4" s="2" t="n"/>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I-007</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Cobro inesperado por el uso de la API de Gemini (PC-IA-01): se usaba la capa gratuita de Google AI Studio y empezó a generar cobros</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Por definir por el equipo: revisar la cuenta y la configuración de la API de Gemini (AI Studio / Vertex AI)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="D5" s="3" t="n"/>
@@ -571,13 +609,9 @@
       <c r="D6" s="2" t="n"/>
       <c r="F6" s="4" t="n"/>
     </row>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="J9" s="5" t="n"/>
     </row>
-    <row r="10"/>
-    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
